--- a/sample_data/수집관리시스템_샘플.xlsx
+++ b/sample_data/수집관리시스템_샘플.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>donor_code</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>남</t>
-  </si>
-  <si>
-    <t>여</t>
   </si>
 </sst>
 </file>
@@ -410,16 +407,16 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>10008</v>
+        <v>10014</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1993</v>
+        <v>1977</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
